--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -463,21 +463,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>218</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3">
@@ -488,21 +488,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>162</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
@@ -543,16 +543,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>312</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -573,11 +573,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -588,21 +588,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>329</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>482</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -638,21 +638,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>270</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -663,21 +663,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>259</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -688,21 +688,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>461</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12">
@@ -718,16 +718,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13">
@@ -738,21 +738,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>465</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14">
@@ -763,21 +763,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228</v>
+        <v>401</v>
       </c>
     </row>
     <row r="15">
@@ -793,16 +793,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>352</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16">
@@ -813,21 +813,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17">
@@ -838,21 +838,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -863,21 +863,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>247</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>178</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
@@ -913,21 +913,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
@@ -948,11 +948,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>122</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22">
@@ -963,21 +963,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23">
@@ -988,21 +988,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24">
@@ -1013,21 +1013,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>167</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25">
@@ -1038,21 +1038,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1063,21 +1063,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
@@ -1088,21 +1088,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>239</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>345</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29">
@@ -1138,21 +1138,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>457</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30">
@@ -1163,21 +1163,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>441</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31">
@@ -1188,21 +1188,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>253</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32">
@@ -1213,21 +1213,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>264</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33">
@@ -1243,16 +1243,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>256</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
@@ -1263,21 +1263,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>332</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35">
@@ -1288,21 +1288,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1318,16 +1318,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>46</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37">
@@ -1338,21 +1338,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>378</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38">
@@ -1363,21 +1363,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>285</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39">
@@ -1388,21 +1388,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>431</v>
+        <v>339</v>
       </c>
     </row>
     <row r="40">
@@ -1413,21 +1413,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>201</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41">
@@ -1438,21 +1438,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>355</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
@@ -1468,16 +1468,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>159</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43">
@@ -1493,16 +1493,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>451</v>
+        <v>358</v>
       </c>
     </row>
     <row r="44">
@@ -1518,16 +1518,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>338</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>463</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46">
@@ -1568,16 +1568,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>398</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47">
@@ -1588,21 +1588,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>243</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48">
@@ -1613,21 +1613,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>98</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>55</v>
+        <v>444</v>
       </c>
     </row>
     <row r="50">
@@ -1663,21 +1663,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="51">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>298</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52">
@@ -1713,21 +1713,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>71</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53">
@@ -1738,21 +1738,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>271</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54">
@@ -1763,21 +1763,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>142</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55">
@@ -1788,21 +1788,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>114</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56">
@@ -1813,21 +1813,21 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>200</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58">
@@ -1863,21 +1863,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>436</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60">
@@ -1913,21 +1913,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>395</v>
+        <v>438</v>
       </c>
     </row>
     <row r="61">
@@ -1943,16 +1943,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>93</v>
+        <v>450</v>
       </c>
     </row>
     <row r="62">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>421</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63">
@@ -1988,21 +1988,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>127</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>250</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -2038,21 +2038,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>184</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66">
@@ -2063,21 +2063,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>413</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67">
@@ -2088,21 +2088,21 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>305</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68">
@@ -2118,16 +2118,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>482</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69">
@@ -2138,21 +2138,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>179</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70">
@@ -2163,21 +2163,21 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>260</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>387</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72">
@@ -2213,21 +2213,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>119</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
@@ -2238,21 +2238,21 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>231</v>
+        <v>389</v>
       </c>
     </row>
     <row r="74">
@@ -2268,16 +2268,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>470</v>
+        <v>216</v>
       </c>
     </row>
     <row r="75">
@@ -2293,16 +2293,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>216</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76">
@@ -2313,21 +2313,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>82</v>
+        <v>316</v>
       </c>
     </row>
     <row r="77">
@@ -2338,21 +2338,21 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>79</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78">
@@ -2363,21 +2363,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>110</v>
+        <v>308</v>
       </c>
     </row>
     <row r="79">
@@ -2388,21 +2388,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80">
@@ -2413,21 +2413,21 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>484</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81">
@@ -2443,16 +2443,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>471</v>
+        <v>410</v>
       </c>
     </row>
     <row r="82">
@@ -2463,21 +2463,21 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>62</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83">
@@ -2493,16 +2493,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>258</v>
+        <v>375</v>
       </c>
     </row>
     <row r="84">
@@ -2513,21 +2513,21 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>208</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85">
@@ -2538,21 +2538,21 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>499</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86">
@@ -2568,16 +2568,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>181</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87">
@@ -2588,21 +2588,21 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
     </row>
     <row r="88">
@@ -2613,21 +2613,21 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>145</v>
+        <v>115</v>
       </c>
     </row>
     <row r="89">
@@ -2638,21 +2638,21 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>269</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -2663,21 +2663,21 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>176</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91">
@@ -2688,21 +2688,21 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>168</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92">
@@ -2713,21 +2713,21 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>289</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93">
@@ -2738,21 +2738,21 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>356</v>
+        <v>317</v>
       </c>
     </row>
     <row r="94">
@@ -2768,16 +2768,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>378</v>
+        <v>286</v>
       </c>
     </row>
     <row r="95">
@@ -2793,16 +2793,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>357</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96">
@@ -2813,21 +2813,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>378</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97">
@@ -2838,21 +2838,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>272</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>276</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99">
@@ -2888,21 +2888,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>280</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100">
@@ -2913,21 +2913,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>123</v>
+        <v>410</v>
       </c>
     </row>
     <row r="101">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>84</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102">
@@ -2963,21 +2963,21 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>215</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103">
@@ -2993,16 +2993,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>244</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -3013,21 +3013,21 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>112</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105">
@@ -3043,16 +3043,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="106">
@@ -3063,21 +3063,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>82</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>493</v>
       </c>
     </row>
     <row r="108">
@@ -3113,21 +3113,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109">
@@ -3138,21 +3138,21 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="110">
@@ -3163,21 +3163,21 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>299</v>
+        <v>483</v>
       </c>
     </row>
     <row r="111">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>337</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112">
@@ -3213,21 +3213,21 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>235</v>
+        <v>142</v>
       </c>
     </row>
     <row r="113">
@@ -3243,16 +3243,16 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>92</v>
+        <v>60</v>
       </c>
     </row>
     <row r="114">
@@ -3263,21 +3263,21 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>394</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115">
@@ -3293,16 +3293,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>362</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116">
@@ -3318,16 +3318,16 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>159</v>
+        <v>252</v>
       </c>
     </row>
     <row r="117">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>160</v>
+        <v>424</v>
       </c>
     </row>
     <row r="118">
@@ -3363,21 +3363,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>212</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119">
@@ -3393,16 +3393,16 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>486</v>
+        <v>326</v>
       </c>
     </row>
     <row r="120">
@@ -3418,16 +3418,16 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>320</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121">
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>500</v>
+        <v>78</v>
       </c>
     </row>
     <row r="122">
@@ -3463,21 +3463,21 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>486</v>
+        <v>246</v>
       </c>
     </row>
     <row r="123">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>416</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124">
@@ -3513,21 +3513,21 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>218</v>
+        <v>41</v>
       </c>
     </row>
     <row r="125">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
@@ -3563,21 +3563,21 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20</v>
+        <v>319</v>
       </c>
     </row>
     <row r="127">
@@ -3588,21 +3588,21 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>187</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128">
@@ -3613,21 +3613,21 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>169</v>
+        <v>291</v>
       </c>
     </row>
     <row r="129">
@@ -3643,16 +3643,16 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>11</v>
+        <v>241</v>
       </c>
     </row>
     <row r="130">
@@ -3663,21 +3663,21 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>388</v>
+        <v>472</v>
       </c>
     </row>
     <row r="131">
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>397</v>
+        <v>166</v>
       </c>
     </row>
     <row r="132">
@@ -3713,21 +3713,21 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>116</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134">
@@ -3763,21 +3763,21 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>404</v>
+        <v>102</v>
       </c>
     </row>
     <row r="135">
@@ -3793,16 +3793,16 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>28</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136">
@@ -3813,21 +3813,21 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>324</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
@@ -3863,21 +3863,21 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="139">
@@ -3893,16 +3893,16 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
     </row>
     <row r="140">
@@ -3913,21 +3913,21 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="141">
@@ -3943,16 +3943,16 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>289</v>
+        <v>486</v>
       </c>
     </row>
     <row r="142">
@@ -3963,21 +3963,21 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="143">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
     </row>
     <row r="144">
@@ -4013,21 +4013,21 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>404</v>
+        <v>124</v>
       </c>
     </row>
     <row r="145">
@@ -4038,21 +4038,21 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>235</v>
+        <v>493</v>
       </c>
     </row>
     <row r="146">
@@ -4063,21 +4063,21 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>456</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147">
@@ -4088,21 +4088,21 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>484</v>
+        <v>215</v>
       </c>
     </row>
     <row r="148">
@@ -4113,21 +4113,21 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>337</v>
+        <v>154</v>
       </c>
     </row>
     <row r="149">
@@ -4143,16 +4143,16 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>198</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
     </row>
     <row r="151">
@@ -4193,16 +4193,16 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>261</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152">
@@ -4213,21 +4213,21 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>112</v>
+        <v>361</v>
       </c>
     </row>
     <row r="153">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>121</v>
+        <v>325</v>
       </c>
     </row>
     <row r="154">
@@ -4263,21 +4263,21 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>36</v>
+        <v>434</v>
       </c>
     </row>
     <row r="155">
@@ -4288,21 +4288,21 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>233</v>
+        <v>122</v>
       </c>
     </row>
     <row r="156">
@@ -4313,21 +4313,21 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>426</v>
+        <v>173</v>
       </c>
     </row>
     <row r="157">
@@ -4338,21 +4338,21 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>81</v>
+        <v>453</v>
       </c>
     </row>
     <row r="158">
@@ -4368,16 +4368,16 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>482</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159">
@@ -4388,21 +4388,21 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>414</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160">
@@ -4418,16 +4418,16 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>116</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161">
@@ -4438,21 +4438,21 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>224</v>
+        <v>376</v>
       </c>
     </row>
     <row r="162">
@@ -4463,21 +4463,21 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>215</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163">
@@ -4488,21 +4488,21 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>114</v>
+        <v>188</v>
       </c>
     </row>
     <row r="164">
@@ -4513,21 +4513,21 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>333</v>
+        <v>457</v>
       </c>
     </row>
     <row r="165">
@@ -4538,21 +4538,21 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>451</v>
+        <v>283</v>
       </c>
     </row>
     <row r="166">
@@ -4563,21 +4563,21 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>497</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>203</v>
+        <v>476</v>
       </c>
     </row>
     <row r="168">
@@ -4618,16 +4618,16 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>64</v>
+        <v>374</v>
       </c>
     </row>
     <row r="169">
@@ -4638,21 +4638,21 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>304</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
     </row>
     <row r="171">
@@ -4688,21 +4688,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>114</v>
+        <v>497</v>
       </c>
     </row>
     <row r="172">
@@ -4713,21 +4713,21 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>468</v>
+        <v>127</v>
       </c>
     </row>
     <row r="173">
@@ -4743,16 +4743,16 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
     </row>
     <row r="174">
@@ -4763,21 +4763,21 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>343</v>
+        <v>402</v>
       </c>
     </row>
     <row r="175">
@@ -4788,21 +4788,21 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>301</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>74</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177">
@@ -4838,21 +4838,21 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="178">
@@ -4863,21 +4863,21 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>387</v>
+        <v>177</v>
       </c>
     </row>
     <row r="179">
@@ -4888,21 +4888,21 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>350</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>113</v>
+        <v>314</v>
       </c>
     </row>
     <row r="181">
@@ -4943,16 +4943,16 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>42</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182">
@@ -4968,16 +4968,16 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>322</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183">
@@ -4988,21 +4988,21 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>326</v>
+        <v>356</v>
       </c>
     </row>
     <row r="184">
@@ -5013,21 +5013,21 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="185">
@@ -5038,21 +5038,21 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>230</v>
+        <v>390</v>
       </c>
     </row>
     <row r="186">
@@ -5063,21 +5063,21 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>458</v>
+        <v>130</v>
       </c>
     </row>
     <row r="187">
@@ -5088,21 +5088,21 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>36</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188">
@@ -5118,16 +5118,16 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>44</v>
+        <v>337</v>
       </c>
     </row>
     <row r="189">
@@ -5138,21 +5138,21 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>334</v>
+        <v>135</v>
       </c>
     </row>
     <row r="190">
@@ -5163,21 +5163,21 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>343</v>
+        <v>485</v>
       </c>
     </row>
     <row r="191">
@@ -5188,21 +5188,21 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>412</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192">
@@ -5213,21 +5213,21 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>229</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193">
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="194">
@@ -5268,16 +5268,16 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="195">
@@ -5288,21 +5288,21 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>420</v>
+        <v>66</v>
       </c>
     </row>
     <row r="196">
@@ -5313,21 +5313,21 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="197">
@@ -5338,21 +5338,21 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>301</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198">
@@ -5363,21 +5363,21 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>207</v>
+        <v>170</v>
       </c>
     </row>
     <row r="199">
@@ -5388,21 +5388,21 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>429</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200">
@@ -5418,16 +5418,16 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>102</v>
+        <v>384</v>
       </c>
     </row>
     <row r="201">
@@ -5443,16 +5443,16 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>261</v>
+        <v>289</v>
       </c>
     </row>
     <row r="202">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>117</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203">
@@ -5488,21 +5488,21 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204">
@@ -5513,21 +5513,21 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>269</v>
+        <v>475</v>
       </c>
     </row>
     <row r="205">
@@ -5538,21 +5538,21 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>434</v>
+        <v>91</v>
       </c>
     </row>
     <row r="206">
@@ -5563,21 +5563,21 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
     </row>
     <row r="207">
@@ -5588,21 +5588,21 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>62</v>
+        <v>410</v>
       </c>
     </row>
     <row r="208">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>262</v>
+        <v>202</v>
       </c>
     </row>
     <row r="209">
@@ -5638,21 +5638,21 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>349</v>
+        <v>187</v>
       </c>
     </row>
     <row r="210">
@@ -5668,16 +5668,16 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>147</v>
+        <v>84</v>
       </c>
     </row>
     <row r="211">
@@ -5693,16 +5693,16 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>278</v>
+        <v>463</v>
       </c>
     </row>
     <row r="212">
@@ -5718,16 +5718,16 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>138</v>
+        <v>296</v>
       </c>
     </row>
     <row r="213">
@@ -5738,21 +5738,21 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>210</v>
+        <v>371</v>
       </c>
     </row>
     <row r="214">
@@ -5768,16 +5768,16 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>351</v>
+        <v>457</v>
       </c>
     </row>
     <row r="215">
@@ -5788,21 +5788,21 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>337</v>
+        <v>163</v>
       </c>
     </row>
     <row r="216">
@@ -5813,21 +5813,21 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>16</v>
+        <v>217</v>
       </c>
     </row>
     <row r="217">
@@ -5838,21 +5838,21 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>334</v>
+        <v>54</v>
       </c>
     </row>
     <row r="218">
@@ -5863,21 +5863,21 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
     </row>
     <row r="219">
@@ -5888,21 +5888,21 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>194</v>
+        <v>306</v>
       </c>
     </row>
     <row r="220">
@@ -5913,21 +5913,21 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>128</v>
+        <v>407</v>
       </c>
     </row>
     <row r="221">
@@ -5938,21 +5938,21 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>466</v>
+        <v>166</v>
       </c>
     </row>
     <row r="222">
@@ -5963,21 +5963,21 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>472</v>
+        <v>197</v>
       </c>
     </row>
     <row r="223">
@@ -5988,21 +5988,21 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>419</v>
+        <v>63</v>
       </c>
     </row>
     <row r="224">
@@ -6018,16 +6018,16 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>355</v>
+        <v>405</v>
       </c>
     </row>
     <row r="225">
@@ -6038,21 +6038,21 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>10</v>
+        <v>306</v>
       </c>
     </row>
     <row r="226">
@@ -6063,21 +6063,21 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>349</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227">
@@ -6088,21 +6088,21 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>215</v>
+        <v>98</v>
       </c>
     </row>
     <row r="228">
@@ -6118,16 +6118,16 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>212</v>
+        <v>418</v>
       </c>
     </row>
     <row r="229">
@@ -6138,21 +6138,21 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>473</v>
+        <v>348</v>
       </c>
     </row>
     <row r="230">
@@ -6163,21 +6163,21 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>46</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231">
@@ -6188,21 +6188,21 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>306</v>
+        <v>70</v>
       </c>
     </row>
     <row r="232">
@@ -6213,21 +6213,21 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>321</v>
+        <v>25</v>
       </c>
     </row>
     <row r="233">
@@ -6238,21 +6238,21 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>113</v>
+        <v>433</v>
       </c>
     </row>
     <row r="234">
@@ -6263,21 +6263,21 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>266</v>
+        <v>241</v>
       </c>
     </row>
     <row r="235">
@@ -6293,16 +6293,16 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>251</v>
+        <v>171</v>
       </c>
     </row>
     <row r="236">
@@ -6318,16 +6318,16 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>24</v>
+        <v>374</v>
       </c>
     </row>
     <row r="237">
@@ -6338,21 +6338,21 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>388</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238">
@@ -6363,21 +6363,21 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>73</v>
+        <v>307</v>
       </c>
     </row>
     <row r="239">
@@ -6388,21 +6388,21 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>427</v>
+        <v>393</v>
       </c>
     </row>
     <row r="240">
@@ -6413,21 +6413,21 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>431</v>
+        <v>194</v>
       </c>
     </row>
     <row r="241">
@@ -6443,16 +6443,16 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>457</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242">
@@ -6463,21 +6463,21 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
     </row>
     <row r="243">
@@ -6488,21 +6488,21 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>387</v>
+        <v>310</v>
       </c>
     </row>
     <row r="244">
@@ -6518,16 +6518,16 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>316</v>
+        <v>425</v>
       </c>
     </row>
     <row r="245">
@@ -6543,16 +6543,16 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>391</v>
+        <v>250</v>
       </c>
     </row>
     <row r="246">
@@ -6563,21 +6563,21 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>357</v>
+        <v>199</v>
       </c>
     </row>
     <row r="247">
@@ -6593,16 +6593,16 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="248">
@@ -6618,16 +6618,16 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>246</v>
+        <v>331</v>
       </c>
     </row>
     <row r="249">
@@ -6638,21 +6638,21 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>288</v>
+        <v>316</v>
       </c>
     </row>
     <row r="250">
@@ -6663,21 +6663,21 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>25</v>
+        <v>364</v>
       </c>
     </row>
     <row r="251">
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="252">
@@ -6713,21 +6713,21 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>439</v>
+        <v>52</v>
       </c>
     </row>
     <row r="253">
@@ -6738,21 +6738,21 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>106</v>
+        <v>485</v>
       </c>
     </row>
     <row r="254">
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="255">
@@ -6793,16 +6793,16 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="256">
@@ -6813,21 +6813,21 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>411</v>
+        <v>481</v>
       </c>
     </row>
     <row r="257">
@@ -6838,21 +6838,21 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>27</v>
+        <v>276</v>
       </c>
     </row>
     <row r="258">
@@ -6863,21 +6863,21 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>324</v>
+        <v>452</v>
       </c>
     </row>
     <row r="259">
@@ -6888,21 +6888,21 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>419</v>
+        <v>79</v>
       </c>
     </row>
     <row r="260">
@@ -6913,21 +6913,21 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>241</v>
+        <v>475</v>
       </c>
     </row>
     <row r="261">
@@ -6938,21 +6938,21 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>142</v>
+        <v>456</v>
       </c>
     </row>
     <row r="262">
@@ -6963,21 +6963,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>433</v>
+        <v>402</v>
       </c>
     </row>
     <row r="263">
@@ -6993,16 +6993,16 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
     </row>
     <row r="264">
@@ -7018,16 +7018,16 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>446</v>
+        <v>413</v>
       </c>
     </row>
     <row r="265">
@@ -7038,21 +7038,21 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>22</v>
+        <v>334</v>
       </c>
     </row>
     <row r="266">
@@ -7063,21 +7063,21 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>441</v>
+        <v>278</v>
       </c>
     </row>
     <row r="267">
@@ -7088,21 +7088,21 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>489</v>
+        <v>215</v>
       </c>
     </row>
     <row r="268">
@@ -7113,21 +7113,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>240</v>
+        <v>61</v>
       </c>
     </row>
     <row r="269">
@@ -7138,21 +7138,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>254</v>
+        <v>364</v>
       </c>
     </row>
     <row r="270">
@@ -7163,21 +7163,21 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>461</v>
+        <v>255</v>
       </c>
     </row>
     <row r="271">
@@ -7193,16 +7193,16 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>146</v>
+        <v>327</v>
       </c>
     </row>
     <row r="272">
@@ -7213,21 +7213,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>462</v>
+        <v>21</v>
       </c>
     </row>
     <row r="273">
@@ -7238,21 +7238,21 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="274">
@@ -7263,21 +7263,21 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>227</v>
+        <v>108</v>
       </c>
     </row>
     <row r="275">
@@ -7293,16 +7293,16 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>94</v>
+        <v>127</v>
       </c>
     </row>
     <row r="276">
@@ -7318,16 +7318,16 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>468</v>
+        <v>45</v>
       </c>
     </row>
     <row r="277">
@@ -7343,16 +7343,16 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>103</v>
+        <v>498</v>
       </c>
     </row>
     <row r="278">
@@ -7368,16 +7368,16 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="279">
@@ -7388,21 +7388,21 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>220</v>
+        <v>392</v>
       </c>
     </row>
     <row r="280">
@@ -7413,21 +7413,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>58</v>
+        <v>423</v>
       </c>
     </row>
     <row r="281">
@@ -7438,21 +7438,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
     </row>
     <row r="282">
@@ -7463,21 +7463,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>152</v>
+        <v>309</v>
       </c>
     </row>
     <row r="283">
@@ -7493,16 +7493,16 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>174</v>
+        <v>319</v>
       </c>
     </row>
     <row r="284">
@@ -7513,21 +7513,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>494</v>
+        <v>181</v>
       </c>
     </row>
     <row r="285">
@@ -7538,21 +7538,21 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>482</v>
+        <v>218</v>
       </c>
     </row>
     <row r="286">
@@ -7563,21 +7563,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>128</v>
+        <v>421</v>
       </c>
     </row>
     <row r="287">
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>161</v>
+        <v>458</v>
       </c>
     </row>
     <row r="288">
@@ -7613,21 +7613,21 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>412</v>
+        <v>290</v>
       </c>
     </row>
     <row r="289">
@@ -7643,16 +7643,16 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>394</v>
+        <v>486</v>
       </c>
     </row>
     <row r="290">
@@ -7668,16 +7668,16 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>305</v>
+        <v>74</v>
       </c>
     </row>
     <row r="291">
@@ -7688,21 +7688,21 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>259</v>
+        <v>429</v>
       </c>
     </row>
     <row r="292">
@@ -7713,21 +7713,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>222</v>
+        <v>488</v>
       </c>
     </row>
     <row r="293">
@@ -7743,16 +7743,16 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>302</v>
+        <v>223</v>
       </c>
     </row>
     <row r="294">
@@ -7763,21 +7763,21 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="295">
@@ -7788,21 +7788,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>176</v>
+        <v>281</v>
       </c>
     </row>
     <row r="296">
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>496</v>
+        <v>347</v>
       </c>
     </row>
     <row r="297">
@@ -7838,21 +7838,21 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Shop B</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>489</v>
+        <v>416</v>
       </c>
     </row>
     <row r="298">
@@ -7863,21 +7863,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>192</v>
+        <v>56</v>
       </c>
     </row>
     <row r="299">
@@ -7888,21 +7888,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>53</v>
+        <v>254</v>
       </c>
     </row>
     <row r="300">
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>455</v>
+        <v>114</v>
       </c>
     </row>
     <row r="301">
@@ -7938,21 +7938,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>453</v>
+        <v>440</v>
       </c>
     </row>
     <row r="302">
@@ -7963,21 +7963,21 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="303">
@@ -7988,21 +7988,21 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>178</v>
+        <v>488</v>
       </c>
     </row>
     <row r="304">
@@ -8013,21 +8013,21 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>440</v>
+        <v>333</v>
       </c>
     </row>
     <row r="305">
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>25</v>
+        <v>229</v>
       </c>
     </row>
     <row r="306">
@@ -8068,16 +8068,16 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>209</v>
+        <v>159</v>
       </c>
     </row>
     <row r="307">
@@ -8088,21 +8088,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>325</v>
+        <v>149</v>
       </c>
     </row>
     <row r="308">
@@ -8118,16 +8118,16 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>432</v>
+        <v>299</v>
       </c>
     </row>
     <row r="309">
@@ -8143,16 +8143,16 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="310">
@@ -8163,21 +8163,21 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>398</v>
+        <v>423</v>
       </c>
     </row>
     <row r="311">
@@ -8188,21 +8188,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>344</v>
+        <v>271</v>
       </c>
     </row>
     <row r="312">
@@ -8218,16 +8218,16 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>32</v>
+        <v>446</v>
       </c>
     </row>
     <row r="313">
@@ -8238,21 +8238,21 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>169</v>
+        <v>461</v>
       </c>
     </row>
     <row r="314">
@@ -8263,21 +8263,21 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>450</v>
+        <v>318</v>
       </c>
     </row>
     <row r="315">
@@ -8293,16 +8293,16 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop G</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>211</v>
+        <v>14</v>
       </c>
     </row>
     <row r="316">
@@ -8313,21 +8313,21 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>11</v>
+        <v>468</v>
       </c>
     </row>
     <row r="317">
@@ -8338,21 +8338,21 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="318">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>173</v>
+        <v>21</v>
       </c>
     </row>
     <row r="319">
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>242</v>
+        <v>496</v>
       </c>
     </row>
     <row r="320">
@@ -8418,16 +8418,16 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="321">
@@ -8443,16 +8443,16 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop M</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>296</v>
+        <v>39</v>
       </c>
     </row>
     <row r="322">
@@ -8463,21 +8463,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>311</v>
+        <v>156</v>
       </c>
     </row>
     <row r="323">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>50</v>
+        <v>428</v>
       </c>
     </row>
     <row r="324">
@@ -8513,21 +8513,21 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>130</v>
+        <v>447</v>
       </c>
     </row>
     <row r="325">
@@ -8538,21 +8538,21 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop A</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>383</v>
+        <v>272</v>
       </c>
     </row>
     <row r="326">
@@ -8563,21 +8563,21 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>281</v>
+        <v>149</v>
       </c>
     </row>
     <row r="327">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>489</v>
+        <v>292</v>
       </c>
     </row>
     <row r="328">
@@ -8618,16 +8618,16 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>311</v>
+        <v>474</v>
       </c>
     </row>
     <row r="329">
@@ -8638,21 +8638,21 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>89</v>
+        <v>355</v>
       </c>
     </row>
     <row r="330">
@@ -8663,21 +8663,21 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>267</v>
+        <v>131</v>
       </c>
     </row>
     <row r="331">
@@ -8688,21 +8688,21 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>306</v>
+        <v>281</v>
       </c>
     </row>
     <row r="332">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>275</v>
+        <v>141</v>
       </c>
     </row>
     <row r="333">
@@ -8738,21 +8738,21 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>474</v>
+        <v>279</v>
       </c>
     </row>
     <row r="334">
@@ -8763,21 +8763,21 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>475</v>
+        <v>29</v>
       </c>
     </row>
     <row r="335">
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>65</v>
+        <v>411</v>
       </c>
     </row>
     <row r="336">
@@ -8813,21 +8813,21 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>137</v>
+        <v>366</v>
       </c>
     </row>
     <row r="337">
@@ -8838,21 +8838,21 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="338">
@@ -8863,21 +8863,21 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Shop F</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>395</v>
+        <v>209</v>
       </c>
     </row>
     <row r="339">
@@ -8893,16 +8893,16 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>276</v>
+        <v>325</v>
       </c>
     </row>
     <row r="340">
@@ -8913,21 +8913,21 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>256</v>
+        <v>464</v>
       </c>
     </row>
     <row r="341">
@@ -8938,21 +8938,21 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>410</v>
+        <v>485</v>
       </c>
     </row>
     <row r="342">
@@ -8963,21 +8963,21 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop C</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>132</v>
+        <v>329</v>
       </c>
     </row>
     <row r="343">
@@ -8988,21 +8988,21 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>213</v>
+        <v>13</v>
       </c>
     </row>
     <row r="344">
@@ -9013,21 +9013,21 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop K</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>92</v>
+        <v>327</v>
       </c>
     </row>
     <row r="345">
@@ -9038,21 +9038,21 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop F</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>397</v>
+        <v>71</v>
       </c>
     </row>
     <row r="346">
@@ -9063,21 +9063,21 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>337</v>
+        <v>36</v>
       </c>
     </row>
     <row r="347">
@@ -9088,21 +9088,21 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Shop H</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>249</v>
+        <v>293</v>
       </c>
     </row>
     <row r="348">
@@ -9113,21 +9113,21 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>66</v>
+        <v>392</v>
       </c>
     </row>
     <row r="349">
@@ -9143,16 +9143,16 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="350">
@@ -9163,21 +9163,21 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>454</v>
+        <v>315</v>
       </c>
     </row>
     <row r="351">
@@ -9188,21 +9188,21 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Shop G</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>36</v>
+        <v>495</v>
       </c>
     </row>
     <row r="352">
@@ -9218,16 +9218,16 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>65</v>
+        <v>328</v>
       </c>
     </row>
     <row r="353">
@@ -9238,21 +9238,21 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>332</v>
+        <v>297</v>
       </c>
     </row>
     <row r="354">
@@ -9263,21 +9263,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>355</v>
+        <v>66</v>
       </c>
     </row>
     <row r="355">
@@ -9288,21 +9288,21 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>396</v>
+        <v>463</v>
       </c>
     </row>
     <row r="356">
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>247</v>
+        <v>477</v>
       </c>
     </row>
     <row r="357">
@@ -9343,16 +9343,16 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>287</v>
+        <v>406</v>
       </c>
     </row>
     <row r="358">
@@ -9363,21 +9363,21 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Shop D</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>432</v>
+        <v>12</v>
       </c>
     </row>
     <row r="359">
@@ -9388,21 +9388,21 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Shop K</t>
+          <t>Shop B</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>458</v>
+        <v>139</v>
       </c>
     </row>
     <row r="360">
@@ -9413,21 +9413,21 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop D</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>56</v>
+        <v>468</v>
       </c>
     </row>
     <row r="361">
@@ -9438,21 +9438,21 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Shop J</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>155</v>
+        <v>416</v>
       </c>
     </row>
     <row r="362">
@@ -9463,21 +9463,21 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Montreal</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Shop C</t>
+          <t>Shop I</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>407</v>
+        <v>376</v>
       </c>
     </row>
     <row r="363">
@@ -9488,21 +9488,21 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Shop E</t>
+          <t>Shop L</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>430</v>
+        <v>303</v>
       </c>
     </row>
     <row r="364">
@@ -9513,21 +9513,21 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Shop M</t>
+          <t>Shop E</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>486</v>
+        <v>33</v>
       </c>
     </row>
     <row r="365">
@@ -9543,16 +9543,16 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Montreal</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Shop I</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>201</v>
+        <v>114</v>
       </c>
     </row>
     <row r="366">
@@ -9563,21 +9563,21 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Shop L</t>
+          <t>Shop H</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>95</v>
+        <v>37</v>
       </c>
     </row>
     <row r="367">
@@ -9588,21 +9588,21 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>London</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Shop A</t>
+          <t>Shop J</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>393</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
